--- a/data/trans_orig/IP25B01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>768</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6080</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2906</t>
+          <t>2982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12236</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15040</t>
+          <t>16091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24826</t>
+          <t>24101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3337</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12869</t>
+          <t>12526</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>14928</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35552</t>
+          <t>35923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17922</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31835</t>
+          <t>32186</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>32340</t>
+          <t>31896</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52807</t>
+          <t>52949</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9515</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>29591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30654</t>
+          <t>30702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30074</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51990</t>
+          <t>54284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30854</t>
+          <t>31863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>152030</t>
+          <t>152596</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44788</t>
+          <t>44837</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100823</t>
+          <t>99056</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>84165</t>
+          <t>83299</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>207349</t>
+          <t>202756</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47029</t>
+          <t>46613</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75028</t>
+          <t>75316</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62119</t>
+          <t>61654</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>94102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117346</t>
+          <t>117522</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157670</t>
+          <t>160876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,71%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>141654</t>
+          <t>138643</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>193899</t>
+          <t>191665</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178427</t>
+          <t>178359</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>224789</t>
+          <t>225334</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>329521</t>
+          <t>337924</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>406931</t>
+          <t>407241</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,31%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>124959</t>
+          <t>127621</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>179021</t>
+          <t>179097</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150199</t>
+          <t>150853</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>193683</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>294793</t>
+          <t>292139</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>359045</t>
+          <t>358565</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,25%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13906</t>
+          <t>13154</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23024</t>
+          <t>23150</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>9957</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22815</t>
+          <t>23540</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15749</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>28404</t>
+          <t>29468</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>50144</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46934</t>
+          <t>45903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66355</t>
+          <t>65246</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54613</t>
+          <t>55281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79977</t>
+          <t>80558</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108515</t>
+          <t>105415</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>141160</t>
+          <t>138156</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57932</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77755</t>
+          <t>76919</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71827</t>
+          <t>71699</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>97447</t>
+          <t>96219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>133960</t>
+          <t>136020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165419</t>
+          <t>168005</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,15%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40415</t>
+          <t>40065</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>160537</t>
+          <t>160677</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57249</t>
+          <t>57571</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>113910</t>
+          <t>115881</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>108906</t>
+          <t>111063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>232754</t>
+          <t>234332</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>73156</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110797</t>
+          <t>110448</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88325</t>
+          <t>87914</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123518</t>
+          <t>124397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172085</t>
+          <t>174409</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>224443</t>
+          <t>228374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,26%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>210840</t>
+          <t>214293</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>270008</t>
+          <t>271413</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>267664</t>
+          <t>268184</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>320955</t>
+          <t>321684</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>496843</t>
+          <t>498128</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>577205</t>
+          <t>577713</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>209288</t>
+          <t>207088</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>266828</t>
+          <t>266262</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251124</t>
+          <t>251236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>300815</t>
+          <t>303049</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>477907</t>
+          <t>474220</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>557328</t>
+          <t>555944</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP25B01_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25B01_2023-Estudios-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de horas al día que emplean en utilizar aparatos electrónicos entre semana / solo 2023 en 2023 (tasa de respuesta: 98,33%)</t>
+          <t>Menores según el número de horas al día que utilizan aparatos electrónicos entre semana en 2023 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5965</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2602</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10995</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,6%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19,54%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2328</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>768</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,63%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>2414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12171</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4433</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16091</t>
+          <t>14026</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6147</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2860</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11299</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>15244</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7780</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24101</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>46,1%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2924</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12526</t>
+          <t>16490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>22395</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14928</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>24585</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>22888</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16867</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>29959</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>40,68%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>29,98%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>53,25%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>18048</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>11063</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24694</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>21,16%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24638</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>14116</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32186</t>
+          <t>26173</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>42686</t>
+          <t>43189</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>31896</t>
+          <t>34194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52949</t>
+          <t>51932</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>51,51%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21257</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15036</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27261</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>37,79%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16664</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>9836</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29591</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>56,6%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>23026</t>
+          <t>11207</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30702</t>
+          <t>16625</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>32464</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>24763</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>40515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -1172,57 +1172,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>56258</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52283</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61426</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>113709</t>
+          <t>100821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>55607</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38588</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>81178</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>58746</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31863</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>152596</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>33,88%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63682</t>
+          <t>35667</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>26066</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>99056</t>
+          <t>47978</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>122428</t>
+          <t>91274</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>83299</t>
+          <t>72098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>202756</t>
+          <t>120511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71420</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59149</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>87270</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>15,16%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>18,52%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>61096</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46613</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>75316</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>75905</t>
+          <t>64544</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61654</t>
+          <t>51827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>80247</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>137002</t>
+          <t>135964</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>117522</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>160876</t>
+          <t>158146</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,7%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>192369</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>169710</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>213515</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>36,01%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>252</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>172134</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>138643</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>191665</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38,22%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>42,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>201837</t>
+          <t>170040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>178359</t>
+          <t>152749</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>225334</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>362409</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337924</t>
+          <t>332402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>407241</t>
+          <t>387881</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,41%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>151832</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133284</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>172201</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>32,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>28,28%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>36,54%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>158375</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>127621</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>179097</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>35,17%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>28,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>39,77%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>170708</t>
+          <t>152118</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>150853</t>
+          <t>134790</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>193683</t>
+          <t>169550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329083</t>
+          <t>303950</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>292139</t>
+          <t>280052</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>358565</t>
+          <t>331975</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,15%</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1741,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>471228</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>471228</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>471228</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>450351</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>450351</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>450351</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>651</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>512132</t>
+          <t>422369</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>512132</t>
+          <t>422369</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>512132</t>
+          <t>422369</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>962483</t>
+          <t>893597</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>962483</t>
+          <t>893597</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>962483</t>
+          <t>893597</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7218</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3530</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7617</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3898</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13154</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3522</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>13819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9846</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23150</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -1971,72 +1971,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>22120</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>14924</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31230</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>8,95%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>18,73%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>15501</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9957</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>23540</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>16,02%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>16005</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15724</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>38462</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>29468</t>
+          <t>28384</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>49795</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60882</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>49592</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>72233</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>36,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>29,75%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>56367</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>45903</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>65246</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>38,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>31,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>44,4%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>67355</t>
+          <t>57858</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>55281</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80558</t>
+          <t>67889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>123722</t>
+          <t>118740</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105415</t>
+          <t>103526</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>138156</t>
+          <t>132969</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>42,29%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>76482</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>65307</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>88367</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>45,88%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>67458</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>57513</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>76919</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>45,91%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>39,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>52,35%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>83617</t>
+          <t>65945</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71699</t>
+          <t>56647</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>96219</t>
+          <t>76756</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>151075</t>
+          <t>142427</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136020</t>
+          <t>128019</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>168005</t>
+          <t>157496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -2310,57 +2310,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>166703</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>146943</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>181502</t>
+          <t>147701</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>328445</t>
+          <t>314404</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2427,72 +2427,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68791</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>51871</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>100354</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>9,91%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>68690</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>40065</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>160677</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>6,17%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24,74%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77863</t>
+          <t>45975</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>57571</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>115881</t>
+          <t>60533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>146553</t>
+          <t>114766</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>111063</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>234332</t>
+          <t>147138</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -2540,72 +2540,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>99687</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>83914</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>118822</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>17,12%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>91842</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>73156</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>110448</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,14%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,26%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>106017</t>
+          <t>91189</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87914</t>
+          <t>76794</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124397</t>
+          <t>108464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>197859</t>
+          <t>190877</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>174409</t>
+          <t>165664</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228374</t>
+          <t>214019</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -2653,72 +2653,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>276140</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>250839</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>300646</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>39,78%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>36,13%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>365</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>246548</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>214293</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>271413</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>37,96%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>32,99%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>41,78%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>293829</t>
+          <t>248198</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>268184</t>
+          <t>227889</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>321684</t>
+          <t>267831</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>540378</t>
+          <t>524338</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>498128</t>
+          <t>493204</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>577713</t>
+          <t>559398</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>249572</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>225149</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>272680</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>32,43%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>39,28%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>371</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>242497</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>207088</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>266262</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>37,33%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>31,88%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>40,99%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>277350</t>
+          <t>229270</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>251236</t>
+          <t>210378</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>303049</t>
+          <t>248543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>519847</t>
+          <t>478842</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>474220</t>
+          <t>448634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>555944</t>
+          <t>510270</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,59%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -2879,57 +2879,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>694190</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>918</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>649577</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>649577</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>649577</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>614633</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>614633</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>755060</t>
+          <t>614633</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1404638</t>
+          <t>1308823</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1404638</t>
+          <t>1308823</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1404638</t>
+          <t>1308823</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
